--- a/03_Outputs/all/idx3_climatico_loadings_y_tops.xlsx
+++ b/03_Outputs/all/idx3_climatico_loadings_y_tops.xlsx
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.64631796805029</v>
+        <v>0.6463179680502905</v>
       </c>
       <c r="D2">
-        <v>0.3752487216349437</v>
+        <v>0.375248721634944</v>
       </c>
       <c r="E2">
         <v>37.5</v>
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.5788114530518104</v>
+        <v>-0.5788114530518089</v>
       </c>
       <c r="D3">
-        <v>0.3360548036140253</v>
+        <v>0.3360548036140245</v>
       </c>
       <c r="E3">
         <v>33.6</v>
@@ -438,10 +438,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>-0.4972427837499467</v>
+        <v>-0.4972427837499474</v>
       </c>
       <c r="D4">
-        <v>0.2886964747510311</v>
+        <v>0.2886964747510315</v>
       </c>
       <c r="E4">
         <v>28.9</v>
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.113110645110351</v>
+        <v>0.1131106451103481</v>
       </c>
       <c r="D5">
-        <v>0.07553506064930832</v>
+        <v>0.07553506064930644</v>
       </c>
       <c r="E5">
         <v>7.6</v>
@@ -480,10 +480,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.5717664519975196</v>
+        <v>-0.5717664519975231</v>
       </c>
       <c r="D6">
-        <v>0.3818244833343296</v>
+        <v>0.3818244833343323</v>
       </c>
       <c r="E6">
         <v>38.2</v>
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>0.8125817536302965</v>
+        <v>0.8125817536302945</v>
       </c>
       <c r="D7">
-        <v>0.5426404560163621</v>
+        <v>0.5426404560163612</v>
       </c>
       <c r="E7">
         <v>54.3</v>
@@ -522,10 +522,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.7546383677882174</v>
+        <v>0.7546383677882171</v>
       </c>
       <c r="D8">
-        <v>0.4601057315806922</v>
+        <v>0.4601057315806916</v>
       </c>
       <c r="E8">
         <v>46</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>0.5814296399274979</v>
+        <v>0.5814296399274954</v>
       </c>
       <c r="D9">
-        <v>0.3544997461838791</v>
+        <v>0.3544997461838773</v>
       </c>
       <c r="E9">
         <v>35.4</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.3040731946024107</v>
+        <v>0.3040731946024148</v>
       </c>
       <c r="D10">
-        <v>0.1853945222354288</v>
+        <v>0.1853945222354311</v>
       </c>
       <c r="E10">
         <v>18.5</v>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.3817332865645336</v>
+        <v>0.3817332865645335</v>
       </c>
     </row>
     <row r="3">
@@ -612,7 +612,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.3201395229319919</v>
+        <v>0.3201395229319922</v>
       </c>
     </row>
     <row r="4">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.2981271905034745</v>
+        <v>0.2981271905034744</v>
       </c>
     </row>
   </sheetData>
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.64631796805029</v>
+        <v>0.6463179680502905</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.5788114530518104</v>
+        <v>-0.5788114530518089</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.4972427837499467</v>
+        <v>-0.4972427837499474</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.8125817536302965</v>
+        <v>0.8125817536302945</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.5717664519975196</v>
+        <v>-0.5717664519975231</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.113110645110351</v>
+        <v>0.1131106451103481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
